--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0171.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0171.xlsx
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Ai thèm quan tâm đến The Order chứ? Mang lại hạnh phúc à? Ta cũng làm được.</t>
+          <t>Ai thèm quan tâm đến The Order chứ? Mang lại hạnh phúc à? Tao cũng làm được.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Chắc là thật. Ta từng thấy một hiệp sĩ của Hội khi còn nhỏ.</t>
+          <t>Chắc là thật. Tao từng thấy một hiệp sĩ của Hội khi còn nhỏ.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Nếu ta bắn lén chúng nó, thì là ta.</t>
+          <t>Nếu tao bắn lén chúng nó, thì là tao.</t>
         </is>
       </c>
     </row>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Đừng có lúc nào cũng "ổn" mà gạt ta sang một bên như thế.</t>
+          <t>Đừng có lúc nào cũng "ổn" mà gạt tao sang một bên như thế.</t>
         </is>
       </c>
     </row>
